--- a/data/output/2025/evaluasi_12.xlsx
+++ b/data/output/2025/evaluasi_12.xlsx
@@ -37,6 +37,10 @@
     <sheet name="1220" sheetId="28" state="visible" r:id="rId28"/>
     <sheet name="1225" sheetId="29" state="visible" r:id="rId29"/>
     <sheet name="1272" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="1204" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="1205" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="1212" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="1216" sheetId="34" state="visible" r:id="rId34"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1060,7 +1064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1120,6 +1124,34 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1206</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Toba</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1134,7 +1166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1222,6 +1254,118 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1207</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Labuhan Batu</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>9.734492949617472</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1207</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Labuhan Batu</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0.2783223577006713</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1207</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Labuhan Batu</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1207</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Labuhan Batu</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-3.98145720345786</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -1236,7 +1380,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1506,18 +1650,242 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D10" t="n">
+        <v>1.0590211737015</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1208</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Asahan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1208</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Asahan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.1675005397326978</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1208</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Asahan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>4.616836984176863</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1208</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Asahan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-1.692338650578745</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1208</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kabupaten Asahan</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-1.094865992212207</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1208</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kabupaten Asahan</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-2.215590094524653</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>1208</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Kabupaten Asahan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.1504772578133937</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pmtb_q4-25_prov vs implisit_y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>1208</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Kabupaten Asahan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
         <v>-2.825897898376403</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_2025</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -1534,7 +1902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1692,18 +2060,158 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>-1.132820959994458</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1209</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Simalungun</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>23.14536559999962</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1209</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Simalungun</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1209</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Simalungun</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>4.992551464165653</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1209</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Simalungun</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2.22317499009316</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1209</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Simalungun</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>-2.497488950600987</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>sog_q_pi_q4-25</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -1720,7 +2228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1920,6 +2428,34 @@
       <c r="F7" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1213</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Langkat</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -1934,7 +2470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2036,18 +2572,130 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1214</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Nias Selatan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.1361728491579119</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1214</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Nias Selatan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2.491050167084017</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1214</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Nias Selatan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.3025363655240195</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1214</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Nias Selatan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
         <v>-2.020584181226865</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_2025</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -2064,7 +2712,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2152,6 +2800,174 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1215</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Humbang Hasundutan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>5.456955842144004</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1215</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Humbang Hasundutan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1215</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Humbang Hasundutan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-1.877062232678543</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1215</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Humbang Hasundutan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.3436111424962537</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1215</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Humbang Hasundutan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.1076155540416259</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pklnprt_q4-25_prov vs c-to-c_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1215</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Humbang Hasundutan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.7732183943294566</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2166,7 +2982,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2254,6 +3070,118 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1219</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Batu Bara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.8310242024589366</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1219</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Batu Bara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>17.261199718844</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1219</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Batu Bara</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1219</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Batu Bara</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-1.27827188647831</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pklnprt_q4-25_prov vs implisit_q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2268,7 +3196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2328,6 +3256,146 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1221</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Padang Lawas</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2.947926496066213</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1221</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Padang Lawas</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1221</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Padang Lawas</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.05229985371560168</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1221</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Padang Lawas</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1.990082184203862</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1221</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Padang Lawas</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.2541919840053979</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pdrb_q4-25_prov vs implisit_q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2342,7 +3410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2402,6 +3470,202 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>Nilai revisi lebih dari (+-4 point) dari nilai rilis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1222</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Labuhan Batu Selatan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>10.1441717854518</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1222</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Labuhan Batu Selatan</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1222</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Labuhan Batu Selatan</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>7.625719088011511</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1222</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Labuhan Batu Selatan</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0.08881381798549567</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1222</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Labuhan Batu Selatan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-2.379628271306129</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1222</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Labuhan Batu Selatan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.04012614774233822</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1222</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Labuhan Batu Selatan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>7.63558769705504</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pdrb_2025_prov vs implisit_y-on-y_pdrb_2025_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -2416,7 +3680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2630,18 +3894,102 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D8" t="n">
+        <v>6.56361913192553</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1210</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Dairi</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1210</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Dairi</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>5.033070718927615</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1210</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Dairi</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>-2.522604481396443</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>sog_q_pi_q4-25</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -2658,7 +4006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2844,20 +4192,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-3.253942997231096</v>
+        <v>-0.7999026192851592</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>sog_q_pi_q4-25</t>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SoG PI lebih dari +-2 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -2872,18 +4220,102 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1223</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Labuhan Batu Utara</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.6410263688912126</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1223</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Labuhan Batu Utara</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-3.253942997231096</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q4-25</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1223</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Labuhan Batu Utara</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>-2.941361560512639</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_2025</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -2900,7 +4332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3030,18 +4462,158 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D5" t="n">
+        <v>9.104087218704898</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1224</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Nias Utara</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1224</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Nias Utara</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.3075861946811754</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1224</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Nias Utara</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2.510453196479769</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1224</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Nias Utara</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.02028173664040268</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1224</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Nias Utara</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
         <v>-2.067121977119414</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_2025</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -3058,7 +4630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3244,18 +4816,214 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D7" t="n">
+        <v>2.846605780492645</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1271</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Sibolga</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>5.979698331344014</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1271</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Sibolga</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1271</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Sibolga</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-2.099070417282663</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1271</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Sibolga</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-1.5001724229372</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1271</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kota Sibolga</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-3.636963252033547</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1271</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kota Sibolga</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.5830586635501156</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1271</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kota Sibolga</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
         <v>-4.628580836420323</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_2025</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -3272,7 +5040,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3360,6 +5128,146 @@
       <c r="F3" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1278</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Gunungsitoli</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1249820452566926</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1278</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Gunungsitoli</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1278</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Gunungsitoli</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-3.920155051260493</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1278</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Gunungsitoli</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.2936805236937848</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1278</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Gunungsitoli</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.2229305772942108</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -3374,7 +5282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3560,20 +5468,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-2.13994517748762</v>
+        <v>0</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>sog_q_pi_q4-25</t>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SoG PI lebih dari +-2 persen</t>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -3588,18 +5496,74 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D8" t="n">
+        <v>0.7460106217782728</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1274</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Tebing Tinggi</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-2.13994517748762</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q4-25</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1274</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Tebing Tinggi</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
         <v>-3.584298971406659</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_2025</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -3616,7 +5580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3774,18 +5738,102 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>9.616700050928323</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1275</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Medan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1275</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Medan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>2.722872209422829</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1275</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Medan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
         <v>-2.50354123329882</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_2025</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -3802,7 +5850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3988,18 +6036,130 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D7" t="n">
+        <v>6.602995803323648</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1211</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Karo</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.5133092777214031</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1211</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Karo</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1211</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Karo</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.00625297108634888</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1211</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Karo</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>-2.025878611708715</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_2025</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -4016,7 +6176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4174,18 +6334,186 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>7.033342990724346</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1218</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Serdang Bedagai</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>1.023703992471358</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1218</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Serdang Bedagai</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1218</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Serdang Bedagai</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-2.698190079069295</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1218</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Serdang Bedagai</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-8.610222437731688</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1218</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Serdang Bedagai</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.02983046759906367</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1218</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Serdang Bedagai</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>-4.326945657430351</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_2025</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -4202,7 +6530,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4262,6 +6590,202 @@
       <c r="F2" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1220</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Padang Lawas Utara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-2.053483562178769</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1220</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Padang Lawas Utara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-0.2867665486958281</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1220</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Padang Lawas Utara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>9.839720907175153</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1220</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Padang Lawas Utara</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.2860558286366395</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1220</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Padang Lawas Utara</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1220</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Padang Lawas Utara</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1.662768458631473</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1220</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Padang Lawas Utara</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.2529468832128627</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -4276,7 +6800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4406,18 +6930,102 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D5" t="n">
+        <v>5.940485390469609</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1225</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Nias Barat</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1225</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Nias Barat</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0.2955705970650263</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1225</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Nias Barat</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
         <v>-2.627750713351903</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>sog_y-on-y_pi_2025</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -4434,7 +7042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4606,6 +7214,146 @@
       <c r="F6" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1273</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Pematang Siantar</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>16.31451986787014</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1273</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Pematang Siantar</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1273</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Pematang Siantar</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-0.1964796448425869</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1273</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Pematang Siantar</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1.25890231283574</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1273</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Pematang Siantar</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.8542996020737714</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -4620,7 +7368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4694,20 +7442,1156 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D3" t="n">
+        <v>-2.137364221852317</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1272</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kota Tanjung Balai</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>-1.614127161791089</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1272</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kota Tanjung Balai</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-2.373230529356726</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1272</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Tanjung Balai</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.04384367372241169</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1272</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Tanjung Balai</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.02334234067209428</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q4-25_prov vs y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1272</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Tanjung Balai</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1272</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Tanjung Balai</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>8.107472521245413</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1272</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Tanjung Balai</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-4.45433125527828</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1272</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Tanjung Balai</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>4.617425729745785</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1272</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kota Tanjung Balai</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.2651402544653397</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1272</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kota Tanjung Balai</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
         <v>-2.059399406776267</v>
       </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>sog_q_pi_q4-25</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1204</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Tapanuli Tengah</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-1.484669897861908</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1204</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Tapanuli Tengah</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-0.01060981316016709</v>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>sog_q_pi_q4-25</t>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>SoG PI lebih dari +-2 persen</t>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1204</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Tapanuli Tengah</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1204</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Tapanuli Tengah</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>6.086835600470771</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1205</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Tapanuli Utara</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-4.311349619514519</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1205</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Tapanuli Utara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>-3.094102626336006</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkrt_q4-25_prov vs q-to-q_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1205</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Tapanuli Utara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>8.773028415483495</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1205</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Tapanuli Utara</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-1.214288712085212</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1205</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Tapanuli Utara</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>-2.119483359957025</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1205</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Tapanuli Utara</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-1.018055596543307</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkrt_q4-25_prov vs y-on-y_pkrt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1205</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Tapanuli Utara</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1205</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Tapanuli Utara</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-3.152878679038368</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1205</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Tapanuli Utara</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-0.2927212742481288</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1212</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Deli Serdang</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>-1.682124981276578</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pdrb_q4-25_prov vs q-to-q_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1212</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Deli Serdang</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>10.55877300932412</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1212</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Deli Serdang</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>37.62426103482898</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1212</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Deli Serdang</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.9186760646231388</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pdrb_q4-25_prov vs y-on-y_pdrb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1212</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kabupaten Deli Serdang</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1212</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Deli Serdang</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-5.471105084756394</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1212</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Deli Serdang</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>-7.795099804792054</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>kode</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>kabupaten/kota</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>periode</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>nilai</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>kolom</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>evaluasi</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1216</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Kabupaten Pakpak Bharat</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>8.984413328121263</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1216</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Kabupaten Pakpak Bharat</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4.663198766114168</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1216</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Pakpak Bharat</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>1216</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Kabupaten Pakpak Bharat</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.009758677566785126</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -4722,7 +8606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4866,6 +8750,314 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>1276</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Kota Binjai</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>15.89807980543461</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1276</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kota Binjai</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.07063940440916013</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1276</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kota Binjai</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1276</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Binjai</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>7.276180882066599</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>y-on-y_pkp_q4-25_prov vs y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1276</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Binjai</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>-4.429704927262987</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1276</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kota Binjai</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-0.3445019058180293</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1276</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kota Binjai</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.4768395974811709</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1276</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kota Binjai</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.3202911536626244</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pkp_q4-25_prov vs implisit_q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1276</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kota Binjai</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.09162120550997589</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_q-to-q_pmtb_q4-25_prov vs implisit_q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>1276</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Kota Binjai</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.1889116152647256</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1276</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Kota Binjai</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.1689998931647492</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_2025_prov vs implisit_y-on-y_pkp_2025_kab</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
         </is>
       </c>
     </row>
@@ -4880,7 +9072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5080,6 +9272,202 @@
       <c r="F7" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1203</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Tapanuli Selatan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>19.74706092225546</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1203</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Tapanuli Selatan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>32.41983559199736</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1203</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Tapanuli Selatan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1203</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Tapanuli Selatan</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>-6.991395044465384</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1203</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Tapanuli Selatan</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-2.794233389786785</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1203</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Tapanuli Selatan</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>7.723597199184007</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_q4-25_prov vs implisit_y-on-y_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>1203</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Kabupaten Tapanuli Selatan</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>6.588843279663278</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>implisit_y-on-y_pkp_2025_prov vs implisit_y-on-y_pkp_2025_kab</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -5094,7 +9482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5322,6 +9710,62 @@
       <c r="F8" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1277</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kota Padang Sidempuan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>5.204909869204749</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1277</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kota Padang Sidempuan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -5336,7 +9780,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5494,18 +9938,130 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>q3-25</t>
+          <t>q4-25</t>
         </is>
       </c>
       <c r="D6" t="n">
+        <v>9.519321882329104</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>1202</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Kabupaten Mandailing Natal</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>17.70259758641721</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1202</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Mandailing Natal</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1202</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Mandailing Natal</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>-3.81309548593805</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>c-to-c_pmtb_q4-25_prov vs c-to-c_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1202</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Mandailing Natal</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
         <v>-2.072441466339216</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>sog_q_pi_q4-25</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>SoG PI lebih dari +-2 persen</t>
         </is>
@@ -5522,7 +10078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5722,6 +10278,174 @@
       <c r="F7" t="inlineStr">
         <is>
           <t>Nilai revisi dan nilai rilis beda arah</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>1217</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Kabupaten Samosir</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>4.899947539412545</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>q-to-q_pklnprt_q4-25_prov vs q-to-q_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>1217</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Kabupaten Samosir</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>0.9299999999999929</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>q-to-q_pkp_q4-25_prov vs q-to-q_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>1217</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Kabupaten Samosir</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>12.06159759266816</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>q-to-q_pmtb_q4-25_prov vs q-to-q_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>1217</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Kabupaten Samosir</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1217</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kabupaten Samosir</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>8.337274605412178</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>y-on-y_pmtb_q4-25_prov vs y-on-y_pmtb_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Beda arah dengan nilai provinsi</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>1217</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabupaten Samosir</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>6.703942280630594</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>c-to-c_pkp_q4-25_prov vs c-to-c_pkp_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
         </is>
       </c>
     </row>
@@ -5736,7 +10460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5827,6 +10551,34 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1201</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Kabupaten Nias</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q4-25</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>y-on-y_pklnprt_q4-25_prov vs y-on-y_pklnprt_q4-25_kab</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Selisih dengan nilai provinsi cukup jauh (+-4 point)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
